--- a/data/trans_dic/P37A$vacunapreferencia-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunapreferencia-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,66</t>
+          <t>2,3; 4,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,63</t>
+          <t>2,2; 4,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,16</t>
+          <t>1,96; 4,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,25</t>
+          <t>5,51; 9,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,64</t>
+          <t>1,84; 3,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,6</t>
+          <t>1,8; 3,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,81</t>
+          <t>1,55; 3,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,47</t>
+          <t>5,86; 8,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,66</t>
+          <t>2,29; 3,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,59</t>
+          <t>2,19; 3,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,65</t>
+          <t>1,99; 3,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,62</t>
+          <t>6,19; 8,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,86</t>
+          <t>1,36; 2,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,98</t>
+          <t>2,25; 3,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,75</t>
+          <t>0,72; 1,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,11</t>
+          <t>6,6; 9,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,98</t>
+          <t>1,44; 3,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,2</t>
+          <t>1,05; 2,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,02</t>
+          <t>0,87; 1,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,17</t>
+          <t>6,77; 8,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,61</t>
+          <t>1,57; 2,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,88</t>
+          <t>1,86; 2,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,65</t>
+          <t>0,92; 1,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,75</t>
+          <t>7,03; 8,62</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,34</t>
+          <t>2,72; 6,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,31</t>
+          <t>1,44; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,77</t>
+          <t>0,74; 3,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,28</t>
+          <t>6,33; 10,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,69</t>
+          <t>2,15; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,53</t>
+          <t>0,65; 3,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,58</t>
+          <t>1,14; 3,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 10,74</t>
+          <t>7,2; 10,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,25</t>
+          <t>2,82; 5,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,43</t>
+          <t>1,28; 3,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,77</t>
+          <t>1,18; 2,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,34</t>
+          <t>7,26; 10,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,45</t>
+          <t>2,24; 3,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,71</t>
+          <t>2,51; 3,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,11</t>
+          <t>1,19; 2,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,27</t>
+          <t>6,84; 8,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,2</t>
+          <t>2,06; 3,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,49</t>
+          <t>1,51; 2,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,32</t>
+          <t>1,44; 2,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,17</t>
+          <t>7,1; 8,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,09</t>
+          <t>2,29; 3,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,89</t>
+          <t>2,14; 2,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,07</t>
+          <t>1,43; 2,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,01</t>
+          <t>7,22; 8,42</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>41967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53583</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>101125</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23788; 48061</t>
+          <t>23736; 46353</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20292; 45088</t>
+          <t>21419; 44647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13885; 31395</t>
+          <t>14752; 32351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30147; 52761</t>
+          <t>31888; 55475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24412; 47876</t>
+          <t>24231; 48860</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24220; 48223</t>
+          <t>24027; 46187</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16247; 37849</t>
+          <t>15453; 37228</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42598; 64008</t>
+          <t>48138; 70820</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53658; 85970</t>
+          <t>53791; 86970</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51360; 83088</t>
+          <t>50727; 83483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35482; 63765</t>
+          <t>34731; 63239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78485; 109567</t>
+          <t>86699; 118352</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154692</t>
+          <t>173302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152132</t>
+          <t>168672</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>306824</t>
+          <t>341974</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23693; 48463</t>
+          <t>23033; 48407</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45003; 78082</t>
+          <t>44284; 75536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15533; 36248</t>
+          <t>14930; 36935</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108681; 185789</t>
+          <t>147146; 201326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23555; 47263</t>
+          <t>22818; 47925</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17315; 38703</t>
+          <t>18439; 40699</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17274; 40209</t>
+          <t>17376; 38861</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>113786; 182899</t>
+          <t>146921; 192596</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50583; 85508</t>
+          <t>51552; 87023</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69821; 107309</t>
+          <t>69341; 106222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37499; 66883</t>
+          <t>37322; 66439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>245662; 351091</t>
+          <t>309269; 379306</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58631</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>115348</t>
+          <t>124086</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14387; 34957</t>
+          <t>14978; 34471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6684; 20728</t>
+          <t>6942; 21784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3991; 15152</t>
+          <t>4072; 16891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42706; 72932</t>
+          <t>45018; 76389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9485; 27092</t>
+          <t>10228; 27933</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2983; 16172</t>
+          <t>2977; 15350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5563; 19679</t>
+          <t>6257; 20405</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47164; 70953</t>
+          <t>52877; 78672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29098; 53913</t>
+          <t>28955; 55946</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12379; 32276</t>
+          <t>11986; 32781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12751; 30329</t>
+          <t>12949; 31775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97594; 135134</t>
+          <t>104983; 145725</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250066</t>
+          <t>274436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>264346</t>
+          <t>292749</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>514412</t>
+          <t>567185</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74819; 113119</t>
+          <t>73364; 111372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85716; 126795</t>
+          <t>85813; 126463</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41729; 71409</t>
+          <t>40334; 71761</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>199253; 285599</t>
+          <t>240985; 309044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67545; 108075</t>
+          <t>69680; 105793</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53873; 88674</t>
+          <t>53610; 86513</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48587; 81938</t>
+          <t>50723; 83115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>220027; 298612</t>
+          <t>264642; 321636</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>151285; 205842</t>
+          <t>152147; 207189</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>147806; 201830</t>
+          <t>149151; 200712</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98494; 143283</t>
+          <t>98753; 142588</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>445984; 569440</t>
+          <t>523338; 610179</t>
         </is>
       </c>
     </row>
